--- a/backend/reports/report.xlsx
+++ b/backend/reports/report.xlsx
@@ -9,18 +9,20 @@
   <sheets>
     <sheet name="Resumen General" sheetId="1" r:id="rId1"/>
     <sheet name="Validación Cruzada" sheetId="2" r:id="rId2"/>
+    <sheet name="Mejores Hiperparámetros" sheetId="3" r:id="rId3"/>
+    <sheet name="Pruebas Estadísticas" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="74">
   <si>
     <t>REPORTE COMPLETO - SIPAKMED-AI</t>
   </si>
   <si>
-    <t>Fecha: 2026-07-13 18:05:47</t>
+    <t>Fecha: 2026-07-13 19:28:48</t>
   </si>
   <si>
     <t>Modelo</t>
@@ -42,6 +44,201 @@
   </si>
   <si>
     <t>MCC (std)</t>
+  </si>
+  <si>
+    <t>MobileNetV2</t>
+  </si>
+  <si>
+    <t>83.50%</t>
+  </si>
+  <si>
+    <t>2.10%</t>
+  </si>
+  <si>
+    <t>0.8100</t>
+  </si>
+  <si>
+    <t>0.0300</t>
+  </si>
+  <si>
+    <t>0.7900</t>
+  </si>
+  <si>
+    <t>0.0400</t>
+  </si>
+  <si>
+    <t>ResNet50</t>
+  </si>
+  <si>
+    <t>93.20%</t>
+  </si>
+  <si>
+    <t>1.50%</t>
+  </si>
+  <si>
+    <t>0.9200</t>
+  </si>
+  <si>
+    <t>0.0200</t>
+  </si>
+  <si>
+    <t>0.8900</t>
+  </si>
+  <si>
+    <t>EfficientNetB0</t>
+  </si>
+  <si>
+    <t>85.30%</t>
+  </si>
+  <si>
+    <t>2.30%</t>
+  </si>
+  <si>
+    <t>0.8300</t>
+  </si>
+  <si>
+    <t>HybridEnsemble</t>
+  </si>
+  <si>
+    <t>93.00%</t>
+  </si>
+  <si>
+    <t>1.20%</t>
+  </si>
+  <si>
+    <t>0.9300</t>
+  </si>
+  <si>
+    <t>HybridMultiscale</t>
+  </si>
+  <si>
+    <t>90.10%</t>
+  </si>
+  <si>
+    <t>1.80%</t>
+  </si>
+  <si>
+    <t>0.8800</t>
+  </si>
+  <si>
+    <t>Mejor Accuracy</t>
+  </si>
+  <si>
+    <t>Learning Rate</t>
+  </si>
+  <si>
+    <t>Weight Decay</t>
+  </si>
+  <si>
+    <t>Batch Size</t>
+  </si>
+  <si>
+    <t>Optimizer</t>
+  </si>
+  <si>
+    <t>0.85%</t>
+  </si>
+  <si>
+    <t>0.001500</t>
+  </si>
+  <si>
+    <t>0.000100</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>AdamW</t>
+  </si>
+  <si>
+    <t>0.94%</t>
+  </si>
+  <si>
+    <t>0.000800</t>
+  </si>
+  <si>
+    <t>0.000010</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>0.87%</t>
+  </si>
+  <si>
+    <t>0.001000</t>
+  </si>
+  <si>
+    <t>0.000050</t>
+  </si>
+  <si>
+    <t>0.93%</t>
+  </si>
+  <si>
+    <t>0.000500</t>
+  </si>
+  <si>
+    <t>0.90%</t>
+  </si>
+  <si>
+    <t>PRUEBAS PARA: ACCURACY</t>
+  </si>
+  <si>
+    <t>Prueba</t>
+  </si>
+  <si>
+    <t>Estadístico</t>
+  </si>
+  <si>
+    <t>p-value</t>
+  </si>
+  <si>
+    <t>Significativo</t>
+  </si>
+  <si>
+    <t>ANOVA</t>
+  </si>
+  <si>
+    <t>78.7880</t>
+  </si>
+  <si>
+    <t>0.000000</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Kruskal-Wallis</t>
+  </si>
+  <si>
+    <t>13.1508</t>
+  </si>
+  <si>
+    <t>0.010562</t>
+  </si>
+  <si>
+    <t>PRUEBAS PARA: F1</t>
+  </si>
+  <si>
+    <t>28.8000</t>
+  </si>
+  <si>
+    <t>0.000018</t>
+  </si>
+  <si>
+    <t>12.4106</t>
+  </si>
+  <si>
+    <t>0.014545</t>
+  </si>
+  <si>
+    <t>PRUEBAS PARA: MCC</t>
+  </si>
+  <si>
+    <t>30.7000</t>
+  </si>
+  <si>
+    <t>0.000014</t>
   </si>
 </sst>
 </file>
@@ -106,10 +303,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -428,7 +628,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -454,6 +654,402 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
